--- a/astro-site/public/dl/plan-negocio-cafeteria/checklist-apertura-cafeteria-brunch.xlsx
+++ b/astro-site/public/dl/plan-negocio-cafeteria/checklist-apertura-cafeteria-brunch.xlsx
@@ -14,7 +14,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F5 - Marketing" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F6 - 90 Dias" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'F1 - Constitucion'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'F2 - Local'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'F3 - Equipamiento'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'F4 - Personal'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'F5 - Marketing'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'F6 - 90 Dias'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +58,11 @@
     <font>
       <name val="Calibri"/>
       <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -91,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,10 +118,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -469,9 +492,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -495,6 +518,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -763,13 +787,53 @@
         <is>
           <t>Si quieres proteger nombre de la cafeteria</t>
         </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>COUNTIF(A5:A13,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E15">
+        <f>COUNTIF(B5:B13,"?*")</f>
+        <v>9.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E13">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -777,9 +841,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -803,6 +867,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1071,13 +1136,53 @@
         <is>
           <t>Cubre incendio, robo, danos por agua, etc.</t>
         </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>COUNTIF(A5:A13,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E15">
+        <f>COUNTIF(B5:B13,"?*")</f>
+        <v>9.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E13">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1085,9 +1190,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1111,6 +1216,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1541,13 +1647,53 @@
         <is>
           <t>Iluminacion calida, plantas, zona Instagram</t>
         </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C21">
+        <f>COUNTIF(A5:A19,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E21">
+        <f>COUNTIF(B5:B19,"?*")</f>
+        <v>15.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E19">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1555,342 +1701,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CHECKLIST APERTURA — CAFETERIA / BRUNCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>FASE 4: PERSONAL Y FORMACION</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>TRAMITE / ACCION</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>PLAZO</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>NOTAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Definir organigrama y turnos</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>1 semana</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Cafeteria: turnos manana (6-15h) y tarde (14-22h)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Publicar ofertas de empleo</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>1-2 semanas</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Buscar baristas con experiencia en specialty coffee</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Seleccion y entrevistas</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2 semanas</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Prueba practica: preparar espresso + latte art</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Contratos de trabajo</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Gestor</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>1 dia</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Convenio provincial hosteleria, verificar categoria</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Alta trabajadores en Seguridad Social</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Gestor</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Antes del alta</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Minimo 1 dia antes de empezar</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Carnet de manipulador de alimentos</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>1 dia</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Obligatorio para todo el personal, curso online valido</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Plan de prevencion de riesgos (PRL)</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>1-2 semanas</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Servicio de Prevencion Ajeno obligatorio</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Formacion barista y cafe</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Titular/Formador</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>1-2 semanas</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Estandarizar extracciones, recetas, limpieza maquina</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Formacion alergenos y APPCC</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>1 dia</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Leches vegetales, gluten, frutos secos — critico en brunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Formacion atencion al cliente</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>1 dia</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Estandares de servicio, reclamaciones, upselling</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1912,10 +1723,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 5: MARKETING Y LANZAMIENTO</t>
-        </is>
-      </c>
-    </row>
+          <t>FASE 4: PERSONAL Y FORMACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1951,22 +1763,22 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Disenar identidad visual (logo, colores, tipografia)</t>
+          <t>Definir organigrama y turnos</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Disenador</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>2-3 semanas</t>
+          <t>1 semana</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Estilo coherente: rustico, moderno, specialty...</t>
+          <t>Cafeteria: turnos manana (6-15h) y tarde (14-22h)</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1790,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Crear pagina web basica</t>
+          <t>Publicar ofertas de empleo</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Disenador/Dev</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1993,7 +1805,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Google My Business es mas urgente que la web</t>
+          <t>Buscar baristas con experiencia en specialty coffee</t>
         </is>
       </c>
     </row>
@@ -2005,7 +1817,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Ficha Google My Business (CRITICO)</t>
+          <t>Seleccion y entrevistas</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -2015,12 +1827,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>2 semanas</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Categoria: Cafeteria. Fotos, horario, menu</t>
+          <t>Prueba practica: preparar espresso + latte art</t>
         </is>
       </c>
     </row>
@@ -2032,12 +1844,12 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Perfiles RRSS (Instagram prioritario)</t>
+          <t>Contratos de trabajo</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Titular</t>
+          <t>Gestor</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2047,7 +1859,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Instagram es el canal #1 para cafeterias/brunch</t>
+          <t>Convenio provincial hosteleria, verificar categoria</t>
         </is>
       </c>
     </row>
@@ -2059,22 +1871,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Sesion fotos profesional</t>
+          <t>Alta trabajadores en Seguridad Social</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Fotografo</t>
+          <t>Gestor</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>Antes del alta</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Fotos de platos brunch, cafe latte art, ambiente</t>
+          <t>Minimo 1 dia antes de empezar</t>
         </is>
       </c>
     </row>
@@ -2086,22 +1898,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Diseno carta / menu board</t>
+          <t>Carnet de manipulador de alimentos</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Disenador</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1 semana</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Carta fisica + pizarra en barra + carta digital QR</t>
+          <t>Obligatorio para todo el personal, curso online valido</t>
         </is>
       </c>
     </row>
@@ -2113,22 +1925,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Rotulacion exterior + vinilo escaparate</t>
+          <t>Plan de prevencion de riesgos (PRL)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Rotulista</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>1 semana</t>
+          <t>1-2 semanas</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Primera impresion desde la calle, fundamental</t>
+          <t>Servicio de Prevencion Ajeno obligatorio</t>
         </is>
       </c>
     </row>
@@ -2140,22 +1952,22 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Campana pre-apertura en RRSS</t>
+          <t>Formacion barista y cafe</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Titular</t>
+          <t>Titular/Formador</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>2-4 semanas</t>
+          <t>1-2 semanas</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Cuenta atras, behind the scenes, sorteo inaugural</t>
+          <t>Estandarizar extracciones, recetas, limpieza maquina</t>
         </is>
       </c>
     </row>
@@ -2167,7 +1979,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Acuerdos con proveedores de cafe</t>
+          <t>Formacion alergenos y APPCC</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -2177,12 +1989,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>2 semanas</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Considerar tostador local — diferencial de marca</t>
+          <t>Leches vegetales, gluten, frutos secos — critico en brunch</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2006,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Registrarse en Google Maps, TripAdvisor</t>
+          <t>Formacion atencion al cliente</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -2209,79 +2021,65 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Tambien TheFork si hay brunch con reservas</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Evento de inauguracion</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>1 dia</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Invitar vecinos, influencers locales, prensa barrio</t>
-        </is>
-      </c>
-    </row>
+          <t>Estandares de servicio, reclamaciones, upselling</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Programa de fidelizacion</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>1 semana</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Tarjeta 10o cafe gratis o app de puntos</t>
-        </is>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>COUNTIF(A5:A14,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E16">
+        <f>COUNTIF(B5:B14,"?*")</f>
+        <v>10.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2301,10 +2099,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 6: PRIMEROS 90 DIAS</t>
-        </is>
-      </c>
-    </row>
+          <t>FASE 5: MARKETING Y LANZAMIENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2340,22 +2139,22 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Revision diaria de caja y ventas</t>
+          <t>Disenar identidad visual (logo, colores, tipografia)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Titular</t>
+          <t>Disenador</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Diario</t>
+          <t>2-3 semanas</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Comparar con previsiones del plan financiero</t>
+          <t>Estilo coherente: rustico, moderno, specialty...</t>
         </is>
       </c>
     </row>
@@ -2367,22 +2166,22 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Control food cost semanal</t>
+          <t>Crear pagina web basica</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Titular</t>
+          <t>Disenador/Dev</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Semanal</t>
+          <t>1-2 semanas</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Pesar y medir: cafe, leche, ingredientes brunch</t>
+          <t>Google My Business es mas urgente que la web</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2193,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Ajustar carta segun ventas reales</t>
+          <t>Ficha Google My Business (CRITICO)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -2404,12 +2203,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Mes 1</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Eliminar lo que no se vende, potenciar bestsellers</t>
+          <t>Categoria: Cafeteria. Fotos, horario, menu</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2220,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Encuestas a clientes (presencial + Google)</t>
+          <t>Perfiles RRSS (Instagram prioritario)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -2431,12 +2230,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Mes 1-3</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Pedir resenas Google, responder TODAS</t>
+          <t>Instagram es el canal #1 para cafeterias/brunch</t>
         </is>
       </c>
     </row>
@@ -2448,22 +2247,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Optimizar turnos de personal</t>
+          <t>Sesion fotos profesional</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Titular</t>
+          <t>Fotografo</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Mes 1-2</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Reforzar pico manana, reducir horas muertas tarde</t>
+          <t>Fotos de platos brunch, cafe latte art, ambiente</t>
         </is>
       </c>
     </row>
@@ -2475,22 +2274,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Revisar proveedores y negociar precios</t>
+          <t>Diseno carta / menu board</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Titular</t>
+          <t>Disenador</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Mes 2</t>
+          <t>1 semana</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Con volumen real, renegociar cafe, leche, bolleria</t>
+          <t>Carta fisica + pizarra en barra + carta digital QR</t>
         </is>
       </c>
     </row>
@@ -2502,22 +2301,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Implementar delivery si hay demanda</t>
+          <t>Rotulacion exterior + vinilo escaparate</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Titular</t>
+          <t>Rotulista</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Mes 2-3</t>
+          <t>1 semana</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Glovo/Uber Eats para brunch take-away</t>
+          <t>Primera impresion desde la calle, fundamental</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2328,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Analizar competencia local</t>
+          <t>Campana pre-apertura en RRSS</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -2539,12 +2338,12 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Mes 1</t>
+          <t>2-4 semanas</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Visitar otras cafeterias de la zona, comparar</t>
+          <t>Cuenta atras, behind the scenes, sorteo inaugural</t>
         </is>
       </c>
     </row>
@@ -2556,22 +2355,22 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Primer cierre contable trimestral</t>
+          <t>Acuerdos con proveedores de cafe</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Gestor</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Mes 3</t>
+          <t>2 semanas</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Comparar P&amp;L real vs plan financiero</t>
+          <t>Considerar tostador local — diferencial de marca</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2382,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Plan de accion correctivo</t>
+          <t>Registrarse en Google Maps, TripAdvisor</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -2593,19 +2392,489 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Mes 3</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Si desviacion &gt;15%, revisar costes y estrategia</t>
-        </is>
+          <t>Tambien TheFork si hay brunch con reservas</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Evento de inauguracion</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>1 dia</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Invitar vecinos, influencers locales, prensa barrio</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Programa de fidelizacion</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Tarjeta 10o cafe gratis o app de puntos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C18">
+        <f>COUNTIF(A5:A16,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E18">
+        <f>COUNTIF(B5:B16,"?*")</f>
+        <v>12.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E16">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CHECKLIST APERTURA — CAFETERIA / BRUNCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FASE 6: PRIMEROS 90 DIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TRAMITE / ACCION</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PLAZO</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>NOTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Revision diaria de caja y ventas</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Diario</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Comparar con previsiones del plan financiero</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Control food cost semanal</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Pesar y medir: cafe, leche, ingredientes brunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Ajustar carta segun ventas reales</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Mes 1</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Eliminar lo que no se vende, potenciar bestsellers</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Encuestas a clientes (presencial + Google)</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Mes 1-3</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Pedir resenas Google, responder TODAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Optimizar turnos de personal</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Mes 1-2</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Reforzar pico manana, reducir horas muertas tarde</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Revisar proveedores y negociar precios</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Mes 2</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Con volumen real, renegociar cafe, leche, bolleria</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Implementar delivery si hay demanda</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Mes 2-3</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Glovo/Uber Eats para brunch take-away</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Analizar competencia local</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Mes 1</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Visitar otras cafeterias de la zona, comparar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Primer cierre contable trimestral</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Mes 3</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Comparar P&amp;L real vs plan financiero</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Plan de accion correctivo</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Mes 3</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Si desviacion &gt;15%, revisar costes y estrategia</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>COUNTIF(A5:A14,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E16">
+        <f>COUNTIF(B5:B14,"?*")</f>
+        <v>10.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:E14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/plan-negocio-cafeteria/checklist-apertura-cafeteria-brunch.xlsx
+++ b/astro-site/public/dl/plan-negocio-cafeteria/checklist-apertura-cafeteria-brunch.xlsx
@@ -7,20 +7,21 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F1 - Constitucion" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F1 - Constitución" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F2 - Local" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F3 - Equipamiento" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F4 - Personal" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F5 - Marketing" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F6 - 90 Dias" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F6 - 90 Días" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'F1 - Constitucion'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'F1 - Constitución'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'F2 - Local'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'F3 - Equipamiento'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'F4 - Personal'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'F5 - Marketing'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'F6 - 90 Dias'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'F6 - 90 Días'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +66,13 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +89,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F5F0E8"/>
         <bgColor rgb="00F5F0E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,16 +130,47 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00C8E6C9"/>
           <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -494,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -507,14 +549,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CHECKLIST APERTURA — CAFETERIA / BRUNCH</t>
+          <t>CHECKLIST APERTURA — CAFETERÍA / BRUNCH</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 1: CONSTITUCION Y TRAMITES LEGALES</t>
+          <t>FASE 1: CONSTITUCIÓN Y TRÁMITES LEGALES</t>
         </is>
       </c>
     </row>
@@ -527,7 +569,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -547,14 +589,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Elegir forma juridica (SL, autonomo)</t>
+          <t>Elegir forma jurídica (SL, autónomo)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -574,14 +616,14 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Constitucion SL ante notario</t>
+          <t>Constitución SL ante notario</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -591,24 +633,24 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1-3 dias</t>
+          <t>1-3 días</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Capital minimo 1 EUR (Ley Crea y Crece)</t>
+          <t>Capital social mínimo de 1 € (Ley 18/2022, Crea y Crece): hay que destinar el 20 % del beneficio a reserva legal hasta que el capital y la reserva sumen 3.000 €, y los socios responden solidariamente de esa diferencia</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Inscripcion en Registro Mercantil</t>
+          <t>Inscripción en Registro Mercantil</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -618,7 +660,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>3-7 dias</t>
+          <t>3-7 días</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -628,7 +670,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -645,24 +687,24 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Epigrafe IAE: 671.4 (cafes y bares sin espectaculos)</t>
+          <t>Epígrafe IAE: Grupo 672 (Cafeterías, por categoría 672.1/672.2/672.3 según el servicio) o 673.2 (Otros cafés y bares; el 673.1 es el de categoría especial) si no hay servicio de mesa; el 671 es de restaurantes</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Alta en Seguridad Social (autonomo + empresa)</t>
+          <t>Alta en Seguridad Social (autónomo + empresa)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -672,17 +714,17 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Tarifa plana autonomos 80 EUR/mes primer ano</t>
+          <t>Cuota según la base mínima del tramo que te corresponda. Consulta el importe del ejercicio en curso y verifica con tu gestoría si te aplica la cuota reducida de inicio de actividad</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -699,7 +741,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1-3 dias</t>
+          <t>1-3 días</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -709,7 +751,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -726,24 +768,24 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>1-3 dias</t>
+          <t>1-3 días</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Imprescindible para tramites telematicos con Hacienda/SS</t>
+          <t>Imprescindible para los trámites telemáticos con Hacienda y con la Seguridad Social</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Registro sanitario RGSEAA (si elaboras)</t>
+          <t>Inscripción en el Registro Sanitario de tu Comunidad Autónoma (declaración responsable de inicio de actividad alimentaria)</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -758,12 +800,12 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Obligatorio si elaboras bolleria propia para venta</t>
+          <t>El Registro General Sanitario estatal (RGSEAA) NO aplica al minorista que sirve al consumidor final (art. 2.2 del RD 191/2011): el que te toca es el autonómico. Sólo necesitas el estatal si vendes tu bollería a otras empresas</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -785,42 +827,102 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Si quieres proteger nombre de la cafeteria</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+          <t>Si quieres proteger nombre de la cafetería</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Registro de actividades de tratamiento de datos personales</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Antes de abrir</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Art. 30 del RGPD y art. 31 de la LOPDGDD: lo pide la AEPD en la primera inspección. Incluye clientes, personal y proveedores</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="75" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Adaptar el TPV y la facturación al sistema Veri*factu / factura electrónica</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Antes de abrir</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>El RD 1007/2023 y su calendario escalonado obligan a que el software de facturación sea verificable. Consulta la fecha que te aplica antes de comprar el TPV que presupuesta la hoja de Inversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C15">
-        <f>COUNTIF(A5:A13,"✓")</f>
+      <c r="C17" s="13">
+        <f>COUNTIF(A5:A15,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E15">
-        <f>COUNTIF(B5:B13,"?*")</f>
-        <v>9.0</v>
+      <c r="E17" s="13">
+        <f>COUNTIF(B5:B15,"?*")-COUNTIF(A5:A15,"N/A")</f>
+        <v>11.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E13">
+  <conditionalFormatting sqref="A5:E15">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A15">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -843,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -856,7 +958,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CHECKLIST APERTURA — CAFETERIA / BRUNCH</t>
+          <t>CHECKLIST APERTURA — CAFETERÍA / BRUNCH</t>
         </is>
       </c>
     </row>
@@ -876,7 +978,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -896,14 +998,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Busqueda y seleccion de local</t>
+          <t>Búsqueda y selección de local</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -918,19 +1020,19 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Buscar zonas con trafico peatonal, oficinas, universidades</t>
+          <t>Busca zonas con tráfico peatonal, oficinas o universidades</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Negociacion contrato alquiler</t>
+          <t>Negociación contrato alquiler</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -945,19 +1047,19 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Renta libre (no LAU para negocio), carencia 2-3 meses</t>
+          <t>La renta y el plazo se pactan libremente (LAU, Título III: arrendamiento para uso distinto de vivienda). Negocia 2-3 meses de carencia mientras dura la obra</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Verificar uso urbanistico (hosteleria)</t>
+          <t>Verificar uso urbanístico (hostelería)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -972,12 +1074,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Pedir informe urbanistico ANTES de firmar</t>
+          <t>Pedir informe urbanístico ANTES de firmar</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -999,19 +1101,19 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Cafeteria sin cocina elaborada = actividad inocua en muchos municipios</t>
+          <t>Cafetería sin cocina elaborada = actividad inocua en muchos municipios</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Declaracion responsable (si aplica)</t>
+          <t>Declaración responsable (si aplica)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1021,17 +1123,17 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>15 dias</t>
+          <t>15 días</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Alternativa a licencia en muchos municipios, mas rapida</t>
+          <t>Alternativa a la licencia en muchos municipios, y más rápida</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1053,12 +1155,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Renovacion anual, tasa municipal variable</t>
+          <t>Renovación anual, tasa municipal variable</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1085,7 +1187,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1102,17 +1204,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Minimo 300.000 EUR RC, obligatorio</t>
+          <t>Mínimo 300.000 € RC, obligatorio</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1129,47 +1231,161 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Cubre incendio, robo, danos por agua, etc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+          <t>Cubre incendio, robo, daños por agua, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Hojas de reclamaciones oficiales y su cartel anunciador</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>1 día</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>El modelo y el texto del cartel los aprueba tu Comunidad Autónoma</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Contrato con gestor autorizado de residuos</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>2 semanas</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Se comprueba en la inspección. Cartón, orgánico y, si fríes, aceite usado, que no puede ir al desagüe</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Contrato de desinsectación, desratización y desinfección (DDD)</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Empresa inscrita en el ROESB; el certificado forma parte del plan APPCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Cartel y contrato de videovigilancia con la empresa de seguridad</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Con la obra</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Cartel homologado en zona visible, contrato de encargado de tratamiento y plazo máximo de conservación de 30 días</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C15">
-        <f>COUNTIF(A5:A13,"✓")</f>
+      <c r="C19" s="13">
+        <f>COUNTIF(A5:A17,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E15">
-        <f>COUNTIF(B5:B13,"?*")</f>
-        <v>9.0</v>
+      <c r="E19" s="13">
+        <f>COUNTIF(B5:B17,"?*")-COUNTIF(A5:A17,"N/A")</f>
+        <v>13.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E13">
+  <conditionalFormatting sqref="A5:E17">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A17">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1205,7 +1421,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CHECKLIST APERTURA — CAFETERIA / BRUNCH</t>
+          <t>CHECKLIST APERTURA — CAFETERÍA / BRUNCH</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1441,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1245,14 +1461,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Proyecto tecnico (si &gt;100m2 o cambio uso)</t>
+          <t>Proyecto técnico (si &gt;100m2 o cambio uso)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1267,12 +1483,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Incluye planos, memoria tecnica, instalaciones</t>
+          <t>Incluye planos, memoria técnica, instalaciones</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1294,19 +1510,19 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Materiales lavables en zona manipulacion</t>
+          <t>Materiales lavables en zona manipulación</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Instalacion electrica (potencia 15-20 kW)</t>
+          <t>Instalación eléctrica (potencia 15-20 kW)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -1321,19 +1537,19 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Maquina cafe + horno + lavavajillas = alto consumo</t>
+          <t>Máquina de café, horno y lavavajillas: es el equipo que dispara el consumo eléctrico</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Fontaneria y evacuacion</t>
+          <t>Fontanería y evacuación</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -1353,14 +1569,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Climatizacion (aire acondicionado + calefaccion)</t>
+          <t>Climatización (aire acondicionado + calefacción)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1380,14 +1596,14 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Compra maquina de cafe profesional</t>
+          <t>Compra de la máquina de café profesional</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -1402,12 +1618,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>2 grupos minimo, considerar contrato con tostador</t>
+          <t>2 grupos mínimo, considerar contrato con tostador</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1434,14 +1650,14 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Compra horno conveccion/combinado</t>
+          <t>Compra horno convección/combinado</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1456,12 +1672,12 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Para bolleria, brunch caliente, tostas</t>
+          <t>Para bollería, brunch caliente, tostas</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1483,12 +1699,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Expositor de tartas, sandwiches, bolleria</t>
+          <t>Expositor de tartas, sándwiches y bollería</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1510,12 +1726,12 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Bajo barra + almacen frigorifico</t>
+          <t>Bajo barra + almacén frigorífico</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1542,7 +1758,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1564,12 +1780,12 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Estilo coherente con concepto, comodo para brunch largo</t>
+          <t>Estilo coherente con el concepto y cómodo para un brunch largo</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1596,14 +1812,14 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Instalacion TPV + software</t>
+          <t>Instalación TPV + software</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1623,14 +1839,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Decoracion e iluminacion</t>
+          <t>Decoración e iluminación</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1645,7 +1861,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Iluminacion calida, plantas, zona Instagram</t>
+          <t>Iluminación cálida, plantas y una zona cuidada para las fotos</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1872,7 @@
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C21">
+      <c r="C21" s="13">
         <f>COUNTIF(A5:A19,"✓")</f>
         <v>0.0</v>
       </c>
@@ -1665,12 +1881,13 @@
           <t>de</t>
         </is>
       </c>
-      <c r="E21">
-        <f>COUNTIF(B5:B19,"?*")</f>
+      <c r="E21" s="13">
+        <f>COUNTIF(B5:B19,"?*")-COUNTIF(A5:A19,"N/A")</f>
         <v>15.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -1679,8 +1896,13 @@
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A19">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1703,7 +1925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1716,14 +1938,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CHECKLIST APERTURA — CAFETERIA / BRUNCH</t>
+          <t>CHECKLIST APERTURA — CAFETERÍA / BRUNCH</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 4: PERSONAL Y FORMACION</t>
+          <t>FASE 4: PERSONAL Y FORMACIÓN</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1958,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1756,7 +1978,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1778,12 +2000,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Cafeteria: turnos manana (6-15h) y tarde (14-22h)</t>
+          <t>Cafetería: turnos mañana (6-15h) y tarde (14-22h)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1810,14 +2032,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Seleccion y entrevistas</t>
+          <t>Selección y entrevistas</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -1832,12 +2054,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Prueba practica: preparar espresso + latte art</t>
+          <t>Prueba práctica: preparar un espresso y un latte art</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1854,17 +2076,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Convenio provincial hosteleria, verificar categoria</t>
+          <t>Convenio provincial hostelería, verificar categoría</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1886,51 +2108,51 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Minimo 1 dia antes de empezar</t>
+          <t>Mínimo 1 día antes de empezar</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Carnet de manipulador de alimentos</t>
+          <t>Formación en higiene alimentaria de todo el equipo</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Obligatorio para todo el personal, curso online valido</t>
+          <t>El «carnet de manipulador» está derogado (RD 109/2010): la formación la acredita la EMPRESA y se documenta en el plan APPCC</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Plan de prevencion de riesgos (PRL)</t>
+          <t>Plan de prevención de riesgos (PRL)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>Titular o servicio ajeno</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1940,19 +2162,19 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Servicio de Prevencion Ajeno obligatorio</t>
+          <t>El plan de prevención es obligatorio; el proveedor externo, no: con menos de 25 trabajadores y un solo centro el titular puede asumir la actividad preventiva (art. 30.5 de la Ley 31/1995 y art. 11 del RD 39/1997)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Formacion barista y cafe</t>
+          <t>Formación barista y café</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1967,19 +2189,19 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Estandarizar extracciones, recetas, limpieza maquina</t>
+          <t>Estandarizar extracciones, recetas y limpieza de la máquina</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Formacion alergenos y APPCC</t>
+          <t>Formación alérgenos y APPCC</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1989,24 +2211,24 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Leches vegetales, gluten, frutos secos — critico en brunch</t>
+          <t>Leches vegetales, gluten, frutos secos — crítico en brunch</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Formacion atencion al cliente</t>
+          <t>Formación atención al cliente</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -2016,47 +2238,107 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Estandares de servicio, reclamaciones, upselling</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="B16" s="8" t="inlineStr">
+          <t>Estándares de servicio, reclamaciones y venta sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Registro horario diario de la jornada de todo el equipo</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Desde el primer contrato</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Art. 34.9 del Estatuto de los Trabajadores; se conserva cuatro años</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Informar al equipo del registro horario y del tratamiento de sus datos</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Desde el primer contrato</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>La cláusula informativa se entrega con el contrato; el fichaje es un tratamiento de datos, no sólo una obligación laboral</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C16">
-        <f>COUNTIF(A5:A14,"✓")</f>
+      <c r="C18" s="13">
+        <f>COUNTIF(A5:A16,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E16">
-        <f>COUNTIF(B5:B14,"?*")</f>
-        <v>10.0</v>
+      <c r="E18" s="13">
+        <f>COUNTIF(B5:B16,"?*")-COUNTIF(A5:A16,"N/A")</f>
+        <v>12.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E14">
+  <conditionalFormatting sqref="A5:E16">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A16">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2079,7 +2361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2092,7 +2374,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CHECKLIST APERTURA — CAFETERIA / BRUNCH</t>
+          <t>CHECKLIST APERTURA — CAFETERÍA / BRUNCH</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2394,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2132,19 +2414,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Disenar identidad visual (logo, colores, tipografia)</t>
+          <t>Diseñar la identidad visual: logotipo, colores y tipografía</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Disenador</t>
+          <t>Diseñador</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -2154,24 +2436,24 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Estilo coherente: rustico, moderno, specialty...</t>
+          <t>Estilo coherente: rústico, moderno, specialty...</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Crear pagina web basica</t>
+          <t>Crear página web básica</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Disenador/Dev</t>
+          <t>Diseñador/Dev</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -2181,19 +2463,19 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Google My Business es mas urgente que la web</t>
+          <t>La ficha de Google es más urgente que la web</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Ficha Google My Business (CRITICO)</t>
+          <t>Ficha Google My Business (CRÍTICO)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -2203,17 +2485,17 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Categoria: Cafeteria. Fotos, horario, menu</t>
+          <t>Categoría: Cafetería. Cuida las fotos, el horario y la carta</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2230,56 +2512,56 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Instagram es el canal #1 para cafeterias/brunch</t>
+          <t>Instagram es el canal #1 para cafeterías/brunch</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Sesion fotos profesional</t>
+          <t>Sesión fotos profesional</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Fotografo</t>
+          <t>Fotógrafo</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Fotos de platos brunch, cafe latte art, ambiente</t>
+          <t>Fotos de platos brunch, café latte art, ambiente</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Diseno carta / menu board</t>
+          <t>Diseño de la carta y de la pizarra de la barra</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Disenador</t>
+          <t>Diseñador</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -2289,19 +2571,19 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Carta fisica + pizarra en barra + carta digital QR</t>
+          <t>Carta física, pizarra en la barra y carta digital con código QR</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Rotulacion exterior + vinilo escaparate</t>
+          <t>Rotulación exterior + vinilo escaparate</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -2316,19 +2598,19 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Primera impresion desde la calle, fundamental</t>
+          <t>Primera impresión desde la calle, fundamental</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Campana pre-apertura en RRSS</t>
+          <t>Campaña pre-apertura en RRSS</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -2343,19 +2625,19 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Cuenta atras, behind the scenes, sorteo inaugural</t>
+          <t>Cuenta atrás, contenido de la puesta a punto y sorteo inaugural</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Acuerdos con proveedores de cafe</t>
+          <t>Acuerdos con proveedores de café</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -2375,7 +2657,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2392,24 +2674,24 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Tambien TheFork si hay brunch con reservas</t>
+          <t>También TheFork si hay brunch con reservas</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Evento de inauguracion</t>
+          <t>Evento de inauguración</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2419,7 +2701,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2429,14 +2711,14 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Programa de fidelizacion</t>
+          <t>Programa de fidelización</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -2451,42 +2733,102 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Tarjeta 10o cafe gratis o app de puntos</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+          <t>Tarjeta de sellos con el décimo café gratis, o aplicación de puntos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Licencia de derechos de autor por la música ambiental</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>2 semanas</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>SGAE y AGEDI-AIE son dos licencias distintas y se pagan las dos</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Cláusula informativa y consentimiento en el sistema de reservas y en la lista de correo</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Antes de abrir</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>TheFork, WhatsApp y newsletter tratan datos: cada canal necesita su información previa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C18">
-        <f>COUNTIF(A5:A16,"✓")</f>
+      <c r="C20" s="13">
+        <f>COUNTIF(A5:A18,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E18">
-        <f>COUNTIF(B5:B16,"?*")</f>
-        <v>12.0</v>
+      <c r="E20" s="13">
+        <f>COUNTIF(B5:B18,"?*")-COUNTIF(A5:A18,"N/A")</f>
+        <v>14.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E16">
+  <conditionalFormatting sqref="A5:E18">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A18">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2522,14 +2864,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CHECKLIST APERTURA — CAFETERIA / BRUNCH</t>
+          <t>CHECKLIST APERTURA — CAFETERÍA / BRUNCH</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 6: PRIMEROS 90 DIAS</t>
+          <t>FASE 6: PRIMEROS 90 DÍAS</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2884,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2562,14 +2904,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Revision diaria de caja y ventas</t>
+          <t>Revisión diaria de caja y ventas</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -2589,7 +2931,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2611,19 +2953,19 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Pesar y medir: cafe, leche, ingredientes brunch</t>
+          <t>Pesar y medir: café, leche, ingredientes brunch</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Ajustar carta segun ventas reales</t>
+          <t>Ajustar carta según ventas reales</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -2643,7 +2985,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2665,12 +3007,12 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Pedir resenas Google, responder TODAS</t>
+          <t>Pedir reseñas Google, responder TODAS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2692,12 +3034,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Reforzar pico manana, reducir horas muertas tarde</t>
+          <t>Reforzar pico mañana, reducir horas muertas tarde</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2719,12 +3061,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Con volumen real, renegociar cafe, leche, bolleria</t>
+          <t>Con volumen real, renegociar café, leche, bollería</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2751,7 +3093,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2773,12 +3115,12 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Visitar otras cafeterias de la zona, comparar</t>
+          <t>Visitar otras cafeterías de la zona, comparar</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2805,14 +3147,14 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Plan de accion correctivo</t>
+          <t>Plan de acción correctivo</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -2827,7 +3169,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Si desviacion &gt;15%, revisar costes y estrategia</t>
+          <t>Si desviación &gt;15%, revisar costes y estrategia</t>
         </is>
       </c>
     </row>
@@ -2838,7 +3180,7 @@
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C16">
+      <c r="C16" s="13">
         <f>COUNTIF(A5:A14,"✓")</f>
         <v>0.0</v>
       </c>
@@ -2847,12 +3189,13 @@
           <t>de</t>
         </is>
       </c>
-      <c r="E16">
-        <f>COUNTIF(B5:B14,"?*")</f>
+      <c r="E16" s="13">
+        <f>COUNTIF(B5:B14,"?*")-COUNTIF(A5:A14,"N/A")</f>
         <v>10.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -2861,8 +3204,13 @@
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A14">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2877,4 +3225,96 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>INSTRUCCIONES DE USO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Este fichero forma parte del producto «plan-negocio-cafeteria» de AI Chef Pro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Las celdas VERDES son las editables: cambia esas y el resto del libro se recalcula solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Columna OK: elige ✓ (hecho), ☐ (pendiente) o N/A (no aplica). Las N/A no cuentan en el total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>El contador de cada pestaña cuenta sólo las ✓; las N/A salen del total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Para editar una celda que no esté en verde: Revisar → Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Más plantillas y kits del catálogo en aichef.pro/productos-digitales</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Versión 2.2 · septiembre 2026 · aichef.pro/plan-negocio-cafeteria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
 </file>